--- a/Documentation/Week 10/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 10/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 10/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ECDA67A-466E-4C88-B3B0-C5A5BB075573}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35E50301-818C-4B0C-AFB2-B4502DADFC08}"/>
   <bookViews>
     <workbookView xWindow="24288" yWindow="1248" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="45">
   <si>
     <t>Wk</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>Coded turning action for gesture</t>
+  </si>
+  <si>
+    <t>Merge project implementation research</t>
   </si>
 </sst>
 </file>
@@ -374,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -411,6 +414,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -431,20 +442,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -530,6 +536,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -870,36 +880,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -919,7 +929,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1789,14 +1799,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2698,33 +2708,67 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B60" s="4"/>
-      <c r="G60" s="6" t="str">
+      <c r="A60" s="1">
+        <v>10</v>
+      </c>
+      <c r="B60" s="4">
+        <v>44833</v>
+      </c>
+      <c r="C60" s="19">
+        <v>0.375</v>
+      </c>
+      <c r="D60" s="4">
+        <v>44833</v>
+      </c>
+      <c r="E60" s="19">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H60" s="1" t="str">
+        <v>2.0000000000582077</v>
+      </c>
+      <c r="H60" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>55.250000000058208</v>
       </c>
       <c r="I60" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.0000000000582077</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B61" s="4"/>
-      <c r="G61" s="6" t="str">
+      <c r="A61" s="1">
+        <v>10</v>
+      </c>
+      <c r="B61" s="4">
+        <v>44833</v>
+      </c>
+      <c r="C61" s="19">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D61" s="4">
+        <v>44833</v>
+      </c>
+      <c r="E61" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H61" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H61" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>56.25</v>
       </c>
       <c r="I61" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
@@ -2776,14 +2820,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3272,14 +3316,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3766,18 +3810,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3791,6 +3823,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
